--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/kimi_kimi-k2.6_judge_high__vs__qwen_qwen3.8-max_judge_medium.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/kimi_kimi-k2.6_judge_high__vs__qwen_qwen3.8-max_judge_medium.xlsx
@@ -2038,33 +2038,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11894.6185419918</v>
+        <v>15178.69962501572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03004196332767606</v>
+        <v>1127.924666972831</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2103,33 +2105,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>65250.51404203987</v>
+        <v>13335.64720803406</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01183303538709879</v>
+        <v>1886.204375012312</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2168,33 +2172,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.007333001121878624</v>
+        <v>12409.07887503272</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02858298830688</v>
+        <v>1476.406957954168</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2233,33 +2239,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.01199997495859861</v>
+        <v>4136.445208976511</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02937501994892955</v>
+        <v>1913.270541001111</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2298,33 +2306,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>68930.92358403374</v>
+        <v>18258.17595800618</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02912501804530621</v>
+        <v>1380.500458006281</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2363,33 +2373,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.004292000085115433</v>
+        <v>11138.99783394299</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01729204086586833</v>
+        <v>1878.571832960006</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2428,33 +2440,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.00866700429469347</v>
+        <v>8621.388832980301</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03766600275412202</v>
+        <v>1917.526083998382</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2493,33 +2507,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.003124994691461325</v>
+        <v>1244.888750021346</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01625000732019544</v>
+        <v>1818.814874975942</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2558,33 +2574,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>4344.456291990355</v>
+        <v>13765.64374996815</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03858399577438831</v>
+        <v>1364.571249985602</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2623,33 +2641,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.00362499849870801</v>
+        <v>12901.54099999927</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01837499439716339</v>
+        <v>1075.738540966995</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2688,33 +2708,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.01079199137166142</v>
+        <v>3754.706209001597</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03195798490196466</v>
+        <v>1680.234416970052</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2753,33 +2775,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.01062499359250069</v>
+        <v>0.005999987479299307</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04083302337676287</v>
+        <v>3701.48629200412</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2818,33 +2842,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>7033.356625004672</v>
+        <v>15748.85883304523</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04483398515731096</v>
+        <v>1601.985374989454</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2883,33 +2909,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>7356.048459012527</v>
+        <v>14385.03737503197</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02429104642942548</v>
+        <v>1474.307959026191</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2948,33 +2976,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.003791006747633219</v>
+        <v>12354.39020901686</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04970800364390016</v>
+        <v>1984.827583015431</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3013,33 +3043,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.004958012141287327</v>
+        <v>8700.766750029288</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0231250305660069</v>
+        <v>1185.708959004842</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3078,33 +3110,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.003917026333510876</v>
+        <v>3383.214500034228</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02112501533702016</v>
+        <v>1331.501541018952</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
